--- a/docs/BT_Tuan07/BaoCaoTienDo_PhanCongNhiemVu.xlsx
+++ b/docs/BT_Tuan07/BaoCaoTienDo_PhanCongNhiemVu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DoAnCNCNPM\DoAnChuyenNganhCongNghePhanMem\docs\BT_Tuan07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59E3C36-F44F-4B4C-A2F8-9491DAED1792}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0C27631-30B9-43D6-B5FF-419ED68A9E8C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -631,7 +631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -704,6 +704,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1133,10 +1136,10 @@
       <c r="E6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="6">
         <v>3</v>
       </c>
       <c r="H6" s="10">
@@ -1145,7 +1148,7 @@
       <c r="I6" s="10">
         <v>46101</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="J6" s="32" t="s">
         <v>23</v>
       </c>
       <c r="K6" s="11" t="s">
@@ -1181,10 +1184,10 @@
       <c r="E7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="6">
         <v>3</v>
       </c>
       <c r="H7" s="10">
@@ -1193,7 +1196,7 @@
       <c r="I7" s="10">
         <v>46101</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="J7" s="32" t="s">
         <v>23</v>
       </c>
       <c r="K7" s="13" t="s">
@@ -1229,10 +1232,10 @@
       <c r="E8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F8" s="3" t="s">
+      <c r="F8" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="6">
         <v>5</v>
       </c>
       <c r="H8" s="10">
@@ -1241,7 +1244,7 @@
       <c r="I8" s="10">
         <v>46101</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="J8" s="32" t="s">
         <v>23</v>
       </c>
       <c r="K8" s="13" t="s">
@@ -1277,10 +1280,10 @@
       <c r="E9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="F9" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="6">
         <v>2</v>
       </c>
       <c r="H9" s="10">
@@ -1289,7 +1292,7 @@
       <c r="I9" s="10">
         <v>46101</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="J9" s="32" t="s">
         <v>23</v>
       </c>
       <c r="K9" s="13" t="s">
@@ -1325,10 +1328,10 @@
       <c r="E10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="3" t="s">
+      <c r="F10" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="6">
         <v>5</v>
       </c>
       <c r="H10" s="10">
@@ -1337,7 +1340,7 @@
       <c r="I10" s="10">
         <v>46101</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="J10" s="32" t="s">
         <v>23</v>
       </c>
       <c r="K10" s="13" t="s">
@@ -1373,10 +1376,10 @@
       <c r="E11" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="F11" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G11" s="3">
+      <c r="G11" s="6">
         <v>2</v>
       </c>
       <c r="H11" s="10">
@@ -1385,7 +1388,7 @@
       <c r="I11" s="10">
         <v>46101</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="J11" s="32" t="s">
         <v>23</v>
       </c>
       <c r="K11" s="13" t="s">
@@ -1423,10 +1426,10 @@
       <c r="E12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="6">
         <v>5</v>
       </c>
       <c r="H12" s="10">
@@ -1435,7 +1438,7 @@
       <c r="I12" s="10">
         <v>46108</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="J12" s="32" t="s">
         <v>47</v>
       </c>
       <c r="K12" s="13" t="s">
@@ -1471,10 +1474,10 @@
       <c r="E13" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="6">
         <v>3</v>
       </c>
       <c r="H13" s="10">
@@ -1483,7 +1486,7 @@
       <c r="I13" s="10">
         <v>46108</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="J13" s="32" t="s">
         <v>47</v>
       </c>
       <c r="K13" s="13" t="s">
@@ -1519,10 +1522,10 @@
       <c r="E14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="F14" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="G14" s="3">
+      <c r="G14" s="6">
         <v>3</v>
       </c>
       <c r="H14" s="10">
@@ -1531,7 +1534,7 @@
       <c r="I14" s="10">
         <v>46108</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="J14" s="32" t="s">
         <v>47</v>
       </c>
       <c r="K14" s="13" t="s">
@@ -1567,10 +1570,10 @@
       <c r="E15" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="F15" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15" s="6">
         <v>3</v>
       </c>
       <c r="H15" s="10">
@@ -1579,7 +1582,7 @@
       <c r="I15" s="10">
         <v>46108</v>
       </c>
-      <c r="J15" s="3" t="s">
+      <c r="J15" s="32" t="s">
         <v>47</v>
       </c>
       <c r="K15" s="13" t="s">
@@ -1615,10 +1618,10 @@
       <c r="E16" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F16" s="3" t="s">
+      <c r="F16" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G16" s="3">
+      <c r="G16" s="6">
         <v>3</v>
       </c>
       <c r="H16" s="10">
@@ -1627,7 +1630,7 @@
       <c r="I16" s="10">
         <v>46108</v>
       </c>
-      <c r="J16" s="3" t="s">
+      <c r="J16" s="32" t="s">
         <v>47</v>
       </c>
       <c r="K16" s="13" t="s">
@@ -1663,10 +1666,10 @@
       <c r="E17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F17" s="3" t="s">
+      <c r="F17" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G17" s="3">
+      <c r="G17" s="6">
         <v>3</v>
       </c>
       <c r="H17" s="10">
@@ -1675,7 +1678,7 @@
       <c r="I17" s="10">
         <v>46108</v>
       </c>
-      <c r="J17" s="3" t="s">
+      <c r="J17" s="32" t="s">
         <v>47</v>
       </c>
       <c r="K17" s="17" t="s">
@@ -1713,15 +1716,15 @@
       <c r="E18" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F18" s="3" t="s">
+      <c r="F18" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G18" s="3">
+      <c r="G18" s="6">
         <v>3</v>
       </c>
       <c r="H18" s="10"/>
       <c r="I18" s="10"/>
-      <c r="J18" s="3"/>
+      <c r="J18" s="32"/>
       <c r="K18" s="17" t="s">
         <v>68</v>
       </c>
@@ -1755,15 +1758,15 @@
       <c r="E19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F19" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="3">
+      <c r="G19" s="6">
         <v>3</v>
       </c>
       <c r="H19" s="10"/>
       <c r="I19" s="10"/>
-      <c r="J19" s="3"/>
+      <c r="J19" s="32"/>
       <c r="K19" s="13" t="s">
         <v>71</v>
       </c>
@@ -1797,15 +1800,15 @@
       <c r="E20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F20" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="3">
+      <c r="G20" s="6">
         <v>5</v>
       </c>
       <c r="H20" s="10"/>
       <c r="I20" s="10"/>
-      <c r="J20" s="3"/>
+      <c r="J20" s="32"/>
       <c r="K20" s="13" t="s">
         <v>74</v>
       </c>
@@ -1839,15 +1842,15 @@
       <c r="E21" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F21" s="3" t="s">
+      <c r="F21" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="3">
+      <c r="G21" s="6">
         <v>3</v>
       </c>
       <c r="H21" s="10"/>
       <c r="I21" s="10"/>
-      <c r="J21" s="3"/>
+      <c r="J21" s="32"/>
       <c r="K21" s="13" t="s">
         <v>77</v>
       </c>
@@ -1881,15 +1884,15 @@
       <c r="E22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F22" s="3" t="s">
+      <c r="F22" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="3">
+      <c r="G22" s="6">
         <v>5</v>
       </c>
       <c r="H22" s="10"/>
       <c r="I22" s="10"/>
-      <c r="J22" s="3"/>
+      <c r="J22" s="32"/>
       <c r="K22" s="13" t="s">
         <v>80</v>
       </c>
@@ -1923,15 +1926,15 @@
       <c r="E23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="F23" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="3">
+      <c r="G23" s="6">
         <v>3</v>
       </c>
       <c r="H23" s="10"/>
       <c r="I23" s="10"/>
-      <c r="J23" s="3"/>
+      <c r="J23" s="32"/>
       <c r="K23" s="13" t="s">
         <v>83</v>
       </c>
@@ -1965,15 +1968,15 @@
       <c r="E24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F24" s="3" t="s">
+      <c r="F24" s="32" t="s">
         <v>54</v>
       </c>
-      <c r="G24" s="3">
+      <c r="G24" s="6">
         <v>2</v>
       </c>
       <c r="H24" s="10"/>
       <c r="I24" s="10"/>
-      <c r="J24" s="3"/>
+      <c r="J24" s="32"/>
       <c r="K24" s="17" t="s">
         <v>86</v>
       </c>
@@ -2007,15 +2010,15 @@
       <c r="E25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F25" s="3" t="s">
+      <c r="F25" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G25" s="3">
+      <c r="G25" s="6">
         <v>3</v>
       </c>
       <c r="H25" s="10"/>
       <c r="I25" s="10"/>
-      <c r="J25" s="3"/>
+      <c r="J25" s="32"/>
       <c r="K25" s="13" t="s">
         <v>89</v>
       </c>
@@ -2049,15 +2052,15 @@
       <c r="E26" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F26" s="3" t="s">
+      <c r="F26" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26" s="6">
         <v>3</v>
       </c>
       <c r="H26" s="10"/>
       <c r="I26" s="10"/>
-      <c r="J26" s="3"/>
+      <c r="J26" s="32"/>
       <c r="K26" s="17" t="s">
         <v>92</v>
       </c>
@@ -2091,15 +2094,15 @@
       <c r="E27" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F27" s="3" t="s">
+      <c r="F27" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G27" s="3">
+      <c r="G27" s="6">
         <v>3</v>
       </c>
       <c r="H27" s="10"/>
       <c r="I27" s="10"/>
-      <c r="J27" s="3"/>
+      <c r="J27" s="32"/>
       <c r="K27" s="17" t="s">
         <v>95</v>
       </c>
@@ -2133,15 +2136,15 @@
       <c r="E28" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F28" s="32" t="s">
         <v>32</v>
       </c>
-      <c r="G28" s="3">
+      <c r="G28" s="6">
         <v>8</v>
       </c>
       <c r="H28" s="10"/>
       <c r="I28" s="10"/>
-      <c r="J28" s="3"/>
+      <c r="J28" s="32"/>
       <c r="K28" s="13" t="s">
         <v>98</v>
       </c>
@@ -2175,15 +2178,15 @@
       <c r="E29" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F29" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G29" s="3">
+      <c r="G29" s="6">
         <v>3</v>
       </c>
       <c r="H29" s="10"/>
       <c r="I29" s="10"/>
-      <c r="J29" s="3"/>
+      <c r="J29" s="32"/>
       <c r="K29" s="17" t="s">
         <v>101</v>
       </c>
@@ -2217,15 +2220,15 @@
       <c r="E30" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="F30" s="3" t="s">
+      <c r="F30" s="32" t="s">
         <v>22</v>
       </c>
-      <c r="G30" s="3">
+      <c r="G30" s="6">
         <v>3</v>
       </c>
       <c r="H30" s="10"/>
       <c r="I30" s="10"/>
-      <c r="J30" s="3"/>
+      <c r="J30" s="32"/>
       <c r="K30" s="17" t="s">
         <v>105</v>
       </c>
@@ -2337,7 +2340,7 @@
       <c r="Y33" s="2"/>
       <c r="Z33" s="2"/>
     </row>
-    <row r="34" spans="1:26" ht="15.75" customHeight="1">
+    <row r="34" spans="1:26" ht="35.25" customHeight="1">
       <c r="A34" s="1"/>
       <c r="B34" s="25" t="s">
         <v>107</v>
